--- a/ncxlxs/pack__ncxlsx__365_어른_어휘.xlsx
+++ b/ncxlxs/pack__ncxlsx__365_어른_어휘.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -539,9 +539,51 @@
         <v>3</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>소솜</v>
+      </c>
+      <c r="B11" t="str">
+        <v>소나기가 한 번 내리는 동안이라는 뜻</v>
+      </c>
+      <c r="C11" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>날파람</v>
+      </c>
+      <c r="B12" t="str">
+        <v>빠르게 날아가는 결에 일어나는 바람</v>
+      </c>
+      <c r="C12" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>노쇠하다</v>
+      </c>
+      <c r="B13" t="str">
+        <v>늙어서 쇠약하고 기운이 별로 없다.</v>
+      </c>
+      <c r="C13" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ncxlxs/pack__ncxlsx__365_어른_어휘.xlsx
+++ b/ncxlxs/pack__ncxlsx__365_어른_어휘.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -581,9 +581,541 @@
         <v>2</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>희떱다</v>
+      </c>
+      <c r="B14" t="str">
+        <v>실속은 없어도 마음이 넓고 손이 크다.</v>
+      </c>
+      <c r="C14" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>몽니</v>
+      </c>
+      <c r="B15" t="str">
+        <v>받고자 하는 대우를 받지 못할 때 내는 실습</v>
+      </c>
+      <c r="C15" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>낭창낭창</v>
+      </c>
+      <c r="B16" t="str">
+        <v>가늘고 긴 막대기나 줄 따위가 자꾸 조금 탄력 있게 흔들리는 모양</v>
+      </c>
+      <c r="C16" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>양감</v>
+      </c>
+      <c r="B17" t="str">
+        <v>양이 있는 느낌, 대상의 부피나 무게의 느낌</v>
+      </c>
+      <c r="C17" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>흥감하다</v>
+      </c>
+      <c r="B18" t="str">
+        <v>마음이 움직여 느끼다.</v>
+      </c>
+      <c r="C18" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>마침맞다</v>
+      </c>
+      <c r="B19" t="str">
+        <v>어떤 경우나 기회에 꼭 알맞다.</v>
+      </c>
+      <c r="C19" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>단견</v>
+      </c>
+      <c r="B20" t="str">
+        <v>짧은 생각이나 의견.</v>
+      </c>
+      <c r="C20" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>시하</v>
+      </c>
+      <c r="B21" t="str">
+        <v>편지글에서 이때, 요즈음의 뜻으로 쓰는 말</v>
+      </c>
+      <c r="C21" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>흔연스럽다</v>
+      </c>
+      <c r="B22" t="str">
+        <v>기쁘거나 반가워 기분이 좋은 듯하다.</v>
+      </c>
+      <c r="C22" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>경도</v>
+      </c>
+      <c r="B23" t="str">
+        <v>온 마음을 기울여 사모하거나 열중함</v>
+      </c>
+      <c r="C23" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>청완하다</v>
+      </c>
+      <c r="B24" t="str">
+        <v>티 없이 맑고 아름답다.</v>
+      </c>
+      <c r="C24" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>슬기주머니</v>
+      </c>
+      <c r="B25" t="str">
+        <v>남다른 재능을 지닌 사람을 비유적으로 이르는 말</v>
+      </c>
+      <c r="C25" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>광휘</v>
+      </c>
+      <c r="B26" t="str">
+        <v>환하고 아름답게 눈이 부심. 또는 그 빛</v>
+      </c>
+      <c r="C26" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>방기하다</v>
+      </c>
+      <c r="B27" t="str">
+        <v>내버리고 아예 돌보지 아니하다.</v>
+      </c>
+      <c r="C27" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>긍휼히</v>
+      </c>
+      <c r="B28" t="str">
+        <v>불쌍하고 가엾게</v>
+      </c>
+      <c r="C28" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>궐기</v>
+      </c>
+      <c r="B29" t="str">
+        <v>벌떡 일어남. 힘차게 일어남</v>
+      </c>
+      <c r="C29" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>호젓하다</v>
+      </c>
+      <c r="B30" t="str">
+        <v>후미져서 무서움을 느낄만큼 고요하다.</v>
+      </c>
+      <c r="C30" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>넨다하다</v>
+      </c>
+      <c r="B31" t="str">
+        <v>어린아이나 아랫사람을 사랑하여 너그럽게 대하다.</v>
+      </c>
+      <c r="C31" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>혜량하다</v>
+      </c>
+      <c r="B32" t="str">
+        <v>남이 헤아려 살펴서 이해하다.</v>
+      </c>
+      <c r="C32" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>소증</v>
+      </c>
+      <c r="B33" t="str">
+        <v>채소따위만 줄곧 먹어서 고기가 몹시 먹고 증세.</v>
+      </c>
+      <c r="C33" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>묵시</v>
+      </c>
+      <c r="B34" t="str">
+        <v>직접적으로 말이나 행동으로 드러내지 않고 은연중에 뜻을 나타내 보임</v>
+      </c>
+      <c r="C34" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>앙살</v>
+      </c>
+      <c r="B35" t="str">
+        <v>엄살을 부리며 버티고 겨루는 짓</v>
+      </c>
+      <c r="C35" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>당주</v>
+      </c>
+      <c r="B36" t="str">
+        <v>지금의 주인</v>
+      </c>
+      <c r="C36" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>안존하다</v>
+      </c>
+      <c r="B37" t="str">
+        <v>얌전하고 조용하다.</v>
+      </c>
+      <c r="C37" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>궤휼</v>
+      </c>
+      <c r="B38" t="str">
+        <v>야릇하고 간사스럽게 속임</v>
+      </c>
+      <c r="C38" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>명리</v>
+      </c>
+      <c r="B39" t="str">
+        <v>명예와 이익을 아울러 이르는 말</v>
+      </c>
+      <c r="C39" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>직조하다</v>
+      </c>
+      <c r="B40" t="str">
+        <v>곧바로 비추다</v>
+      </c>
+      <c r="C40" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>침잠</v>
+      </c>
+      <c r="B41" t="str">
+        <v>겉으로 드러나지 아니하게 물속 깊숙이 가라앚거나 숨음</v>
+      </c>
+      <c r="C41" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>시혜</v>
+      </c>
+      <c r="B42" t="str">
+        <v>은혜를 베풂, 또는 그 은혜</v>
+      </c>
+      <c r="C42" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>교치성</v>
+      </c>
+      <c r="B43" t="str">
+        <v>일이나 동작을 정교하고 치밀하게 수행하는 능력</v>
+      </c>
+      <c r="C43" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>심상하다</v>
+      </c>
+      <c r="B44" t="str">
+        <v>대수롭지 않고 예사롭다.</v>
+      </c>
+      <c r="C44" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>필담</v>
+      </c>
+      <c r="B45" t="str">
+        <v>음성언어가 아닌 문자언어로 대화를 주고 받는 것</v>
+      </c>
+      <c r="C45" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>지리멸렬</v>
+      </c>
+      <c r="B46" t="str">
+        <v>이리저리 흩어지고 찢기어 갈피를 잡을 수 없음</v>
+      </c>
+      <c r="C46" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>암팡지다</v>
+      </c>
+      <c r="B47" t="str">
+        <v>몸은 작아도 힘차고 다부지다.</v>
+      </c>
+      <c r="C47" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>무렴하다</v>
+      </c>
+      <c r="B48" t="str">
+        <v>염치가 없어 마음이 부끄럽고 거북하다.</v>
+      </c>
+      <c r="C48" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>면구하다</v>
+      </c>
+      <c r="B49" t="str">
+        <v>낯을 들고 대하기가 부끄럽다.</v>
+      </c>
+      <c r="C49" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>격랑</v>
+      </c>
+      <c r="B50" t="str">
+        <v>거센 파도,  모질고 어려운 시련</v>
+      </c>
+      <c r="C50" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>분수령</v>
+      </c>
+      <c r="B51" t="str">
+        <v>어떤 사실이나 사태가 발전하는 전환점</v>
+      </c>
+      <c r="C51" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D51">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ncxlxs/pack__ncxlsx__365_어른_어휘.xlsx
+++ b/ncxlxs/pack__ncxlsx__365_어른_어휘.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D96"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -600,7 +600,7 @@
         <v>몽니</v>
       </c>
       <c r="B15" t="str">
-        <v>받고자 하는 대우를 받지 못할 때 내는 실습</v>
+        <v>받고자 하는 대우를 받지 못할 때 내는 심술</v>
       </c>
       <c r="C15" t="str">
         <v>365 어른 어휘</v>
@@ -1113,9 +1113,639 @@
         <v>2</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>눌변</v>
+      </c>
+      <c r="B52" t="str">
+        <v>더듬거리는 서툰 말솜씨</v>
+      </c>
+      <c r="C52" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>숭고</v>
+      </c>
+      <c r="B53" t="str">
+        <v>뜻이 높고 고상하다.</v>
+      </c>
+      <c r="C53" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>혜안</v>
+      </c>
+      <c r="B54" t="str">
+        <v>사물을 꿰뚫어 보는 안목과 식견</v>
+      </c>
+      <c r="C54" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>미맹</v>
+      </c>
+      <c r="B55" t="str">
+        <v>맛을 보는 감각에 장애가 있는 상태</v>
+      </c>
+      <c r="C55" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>표착하다</v>
+      </c>
+      <c r="B56" t="str">
+        <v>정처 없이 떠돌아 다니다가 일정한 곳에 정착하다.</v>
+      </c>
+      <c r="C56" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>석별</v>
+      </c>
+      <c r="B57" t="str">
+        <v>서로 애틋하게 이별함</v>
+      </c>
+      <c r="C57" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>꽃샘바람</v>
+      </c>
+      <c r="B58" t="str">
+        <v>봄철 꽃이 필 무렵에 부는 찬 바람</v>
+      </c>
+      <c r="C58" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>모꼬지</v>
+      </c>
+      <c r="B59" t="str">
+        <v>놀이나 잔치 등으로 여러 사람이 모이는 일</v>
+      </c>
+      <c r="C59" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>해토머리</v>
+      </c>
+      <c r="B60" t="str">
+        <v>얼었던 땅이 녹아서 풀리기 시작할 때</v>
+      </c>
+      <c r="C60" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>녹지근하다</v>
+      </c>
+      <c r="B61" t="str">
+        <v>온몸에 힘이 없고 맥이 풀려 몹시 나른하다.</v>
+      </c>
+      <c r="C61" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>명징</v>
+      </c>
+      <c r="B62" t="str">
+        <v>깨끗하고 맑다.</v>
+      </c>
+      <c r="C62" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>자발떨다</v>
+      </c>
+      <c r="B63" t="str">
+        <v>행동이 가볍고 참을성이 없음을 겉으로 나타내다.</v>
+      </c>
+      <c r="C63" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>참칭하다</v>
+      </c>
+      <c r="B64" t="str">
+        <v>분수에 넘치는 칭호를 스스로 이르다.</v>
+      </c>
+      <c r="C64" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>순리</v>
+      </c>
+      <c r="B65" t="str">
+        <v>순한 이치나 도리.</v>
+      </c>
+      <c r="C65" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>여반장</v>
+      </c>
+      <c r="B66" t="str">
+        <v>손바닥을 뒤집는 것 같다. 일이 매우 쉽다.</v>
+      </c>
+      <c r="C66" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>호오</v>
+      </c>
+      <c r="B67" t="str">
+        <v>좋음과 싫음</v>
+      </c>
+      <c r="C67" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>가관</v>
+      </c>
+      <c r="B68" t="str">
+        <v>꼴이 볼만하다.</v>
+      </c>
+      <c r="C68" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>기름하다</v>
+      </c>
+      <c r="B69" t="str">
+        <v>조금 긴 듯하다.</v>
+      </c>
+      <c r="C69" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>미혹</v>
+      </c>
+      <c r="B70" t="str">
+        <v>무엇에 홀려 정신을 차리지 못함.</v>
+      </c>
+      <c r="C70" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>살풍경</v>
+      </c>
+      <c r="B71" t="str">
+        <v>보잘것 없이 메마르고 스산한 풍경</v>
+      </c>
+      <c r="C71" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>상서롭다</v>
+      </c>
+      <c r="B72" t="str">
+        <v>복되고 길한 일이 일어날 조짐이 있다.</v>
+      </c>
+      <c r="C72" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>감응하다</v>
+      </c>
+      <c r="B73" t="str">
+        <v>어떤 느낌을 받아 마음이 따라 움직이다.</v>
+      </c>
+      <c r="C73" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>마뜩하다</v>
+      </c>
+      <c r="B74" t="str">
+        <v>제법 마음에 들 만하다.</v>
+      </c>
+      <c r="C74" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>부아</v>
+      </c>
+      <c r="B75" t="str">
+        <v>노엽거나 분한 마음</v>
+      </c>
+      <c r="C75" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>자몽하다</v>
+      </c>
+      <c r="B76" t="str">
+        <v>졸릴 때처럼 정신이 흐릿한 상태이다.</v>
+      </c>
+      <c r="C76" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>헛헛하다</v>
+      </c>
+      <c r="B77" t="str">
+        <v>채워지지 않은 허전한 느낌이 있다.</v>
+      </c>
+      <c r="C77" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>공수표</v>
+      </c>
+      <c r="B78" t="str">
+        <v>실행이 없는 약속을 비유적으로 이르는 말</v>
+      </c>
+      <c r="C78" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>마수걸이</v>
+      </c>
+      <c r="B79" t="str">
+        <v>맨 처음으로 물건을 팔아 얻는 소득</v>
+      </c>
+      <c r="C79" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>너울가지</v>
+      </c>
+      <c r="B80" t="str">
+        <v>남과 잘 사귀는 솜씨</v>
+      </c>
+      <c r="C80" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>대거리</v>
+      </c>
+      <c r="B81" t="str">
+        <v>상대편에게 맞서서 대듦</v>
+      </c>
+      <c r="C81" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>몽글하다</v>
+      </c>
+      <c r="B82" t="str">
+        <v>감정이 복받치어 가슴이 갑자기 꽉 차는 듯하다.</v>
+      </c>
+      <c r="C82" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>도탑다</v>
+      </c>
+      <c r="B83" t="str">
+        <v>서로의 관계에 사랑이나 인정이 많고 깊다.</v>
+      </c>
+      <c r="C83" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>답청</v>
+      </c>
+      <c r="B84" t="str">
+        <v>봄에 파랗게 난 풀을 밟으며 산책함.</v>
+      </c>
+      <c r="C84" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>멸칭</v>
+      </c>
+      <c r="B85" t="str">
+        <v>경멸하여 일컬음. 또는 그렇게 부르는 말</v>
+      </c>
+      <c r="C85" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>난연하다</v>
+      </c>
+      <c r="B86" t="str">
+        <v>빛나는 것이 밝다.</v>
+      </c>
+      <c r="C86" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>사고무친</v>
+      </c>
+      <c r="B87" t="str">
+        <v>의지할 만한 사람이 아무도 없음.</v>
+      </c>
+      <c r="C87" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>서름하다</v>
+      </c>
+      <c r="B88" t="str">
+        <v>남과 가깝지 못하고 사이가 조금 서먹하다.</v>
+      </c>
+      <c r="C88" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>알음알이</v>
+      </c>
+      <c r="B89" t="str">
+        <v>약살빠른 수단, 서로 가까이 아는 사람.</v>
+      </c>
+      <c r="C89" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>친선</v>
+      </c>
+      <c r="B90" t="str">
+        <v>서로 간에 친밀하여 사이가 좋음</v>
+      </c>
+      <c r="C90" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>된서리</v>
+      </c>
+      <c r="B91" t="str">
+        <v>늦가을에 아주 되게 내리는 서리.</v>
+      </c>
+      <c r="C91" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>밑글</v>
+      </c>
+      <c r="B92" t="str">
+        <v>이미 알고 있어 밑천이 되는 글</v>
+      </c>
+      <c r="C92" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>바특하다</v>
+      </c>
+      <c r="B93" t="str">
+        <v>두 대상이나 물체 사이가 조금 가깝다.</v>
+      </c>
+      <c r="C93" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>잡도리</v>
+      </c>
+      <c r="B94" t="str">
+        <v>단단히 준비하거나 대책을 세움, 엄하게 단속하는 일.</v>
+      </c>
+      <c r="C94" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>하릴없이</v>
+      </c>
+      <c r="B95" t="str">
+        <v>달리 어떻게 할 도리가 없이.</v>
+      </c>
+      <c r="C95" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>귀물스럽다</v>
+      </c>
+      <c r="B96" t="str">
+        <v>귀중한 물건인 듯하다. 드물어서 얻기 어렵다.</v>
+      </c>
+      <c r="C96" t="str">
+        <v>365 어른 어휘</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D96"/>
   </ignoredErrors>
 </worksheet>
 </file>